--- a/Overture-Match-Suggestions/ZM.xlsx
+++ b/Overture-Match-Suggestions/ZM.xlsx
@@ -638,10 +638,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Chibombo District</t>
+        </is>
+      </c>
       <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
@@ -736,10 +750,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Kapiri Mposhi District</t>
+        </is>
+      </c>
       <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="n"/>
       <c r="S3" s="2" t="n"/>
@@ -834,10 +862,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Mumbwa District</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="n"/>
       <c r="S4" s="2" t="n"/>
@@ -932,10 +974,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Kabwe District</t>
+        </is>
+      </c>
       <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="n"/>
       <c r="S5" s="2" t="n"/>
@@ -1030,10 +1086,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Mkushi District</t>
+        </is>
+      </c>
       <c r="Q6" s="2" t="n"/>
       <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
@@ -1128,10 +1198,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Chisamba District</t>
+        </is>
+      </c>
       <c r="Q7" s="2" t="n"/>
       <c r="R7" s="2" t="n"/>
       <c r="S7" s="2" t="n"/>
@@ -1226,10 +1310,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Serenje District</t>
+        </is>
+      </c>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="2" t="n"/>
       <c r="S8" s="2" t="n"/>
@@ -1324,10 +1422,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Chitambo District</t>
+        </is>
+      </c>
       <c r="Q9" s="2" t="n"/>
       <c r="R9" s="2" t="n"/>
       <c r="S9" s="2" t="n"/>
@@ -1422,10 +1534,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Shibuyunji District</t>
+        </is>
+      </c>
       <c r="Q10" s="2" t="n"/>
       <c r="R10" s="2" t="n"/>
       <c r="S10" s="2" t="n"/>
@@ -1520,10 +1646,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Luano District</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="n"/>
       <c r="R11" s="2" t="n"/>
       <c r="S11" s="2" t="n"/>
@@ -1618,10 +1758,24 @@
           <t>CentralZambia</t>
         </is>
       </c>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>ZM-02</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Ngabwe District</t>
+        </is>
+      </c>
       <c r="Q12" s="2" t="n"/>
       <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
@@ -1722,10 +1876,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>Kitwe District</t>
+        </is>
+      </c>
       <c r="Q13" s="2" t="n"/>
       <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
@@ -1826,10 +1994,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Ndola District</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="n"/>
       <c r="R14" s="2" t="n"/>
       <c r="S14" s="2" t="n"/>
@@ -1924,10 +2106,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>Chingola District</t>
+        </is>
+      </c>
       <c r="Q15" s="2" t="n"/>
       <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
@@ -2022,10 +2218,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Luanshya District</t>
+        </is>
+      </c>
       <c r="Q16" s="2" t="n"/>
       <c r="R16" s="2" t="n"/>
       <c r="S16" s="2" t="n"/>
@@ -2120,10 +2330,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>Mufulira District</t>
+        </is>
+      </c>
       <c r="Q17" s="2" t="n"/>
       <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
@@ -2218,10 +2442,22 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M18" s="2" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>locality</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>Masaiti</t>
+        </is>
+      </c>
       <c r="Q18" s="2" t="n"/>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
@@ -2314,10 +2550,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Kalulushi District</t>
+        </is>
+      </c>
       <c r="Q19" s="2" t="n"/>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
@@ -2412,10 +2662,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n"/>
-      <c r="P20" s="2" t="n"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>Chililabombwe District</t>
+        </is>
+      </c>
       <c r="Q20" s="2" t="n"/>
       <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
@@ -2510,10 +2774,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="n"/>
-      <c r="P21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Mpongwe District</t>
+        </is>
+      </c>
       <c r="Q21" s="2" t="n"/>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
@@ -2608,10 +2886,24 @@
           <t>CopperbeltZambia</t>
         </is>
       </c>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="2" t="n"/>
-      <c r="O22" s="2" t="n"/>
-      <c r="P22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>ZM-08</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>Lufwanyama District</t>
+        </is>
+      </c>
       <c r="Q22" s="2" t="n"/>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
@@ -2712,10 +3004,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M23" s="2" t="n"/>
-      <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n"/>
-      <c r="P23" s="2" t="n"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>Chipata District</t>
+        </is>
+      </c>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
@@ -2810,10 +3116,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M24" s="2" t="n"/>
-      <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n"/>
-      <c r="P24" s="2" t="n"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>Petauke District</t>
+        </is>
+      </c>
       <c r="Q24" s="2" t="n"/>
       <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
@@ -2908,10 +3228,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M25" s="2" t="n"/>
-      <c r="N25" s="2" t="n"/>
-      <c r="O25" s="2" t="n"/>
-      <c r="P25" s="2" t="n"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>Katete District</t>
+        </is>
+      </c>
       <c r="Q25" s="2" t="n"/>
       <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
@@ -3006,10 +3340,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M26" s="2" t="n"/>
-      <c r="N26" s="2" t="n"/>
-      <c r="O26" s="2" t="n"/>
-      <c r="P26" s="2" t="n"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>Sinda District</t>
+        </is>
+      </c>
       <c r="Q26" s="2" t="n"/>
       <c r="R26" s="2" t="n"/>
       <c r="S26" s="2" t="n"/>
@@ -3104,10 +3452,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M27" s="2" t="n"/>
-      <c r="N27" s="2" t="n"/>
-      <c r="O27" s="2" t="n"/>
-      <c r="P27" s="2" t="n"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>Chipangali District</t>
+        </is>
+      </c>
       <c r="Q27" s="2" t="n"/>
       <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
@@ -3202,10 +3564,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M28" s="2" t="n"/>
-      <c r="N28" s="2" t="n"/>
-      <c r="O28" s="2" t="n"/>
-      <c r="P28" s="2" t="n"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>Lumezi District</t>
+        </is>
+      </c>
       <c r="Q28" s="2" t="n"/>
       <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
@@ -3300,10 +3676,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n"/>
-      <c r="P29" s="2" t="n"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>Kasenengwa District</t>
+        </is>
+      </c>
       <c r="Q29" s="2" t="n"/>
       <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
@@ -3398,10 +3788,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
-      <c r="P30" s="2" t="n"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>Lundazi District</t>
+        </is>
+      </c>
       <c r="Q30" s="2" t="n"/>
       <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
@@ -3496,10 +3900,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n"/>
-      <c r="P31" s="2" t="n"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>Chama District</t>
+        </is>
+      </c>
       <c r="Q31" s="2" t="n"/>
       <c r="R31" s="2" t="n"/>
       <c r="S31" s="2" t="n"/>
@@ -3594,10 +4012,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n"/>
-      <c r="P32" s="2" t="n"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>Nyimba District</t>
+        </is>
+      </c>
       <c r="Q32" s="2" t="n"/>
       <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
@@ -3692,10 +4124,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M33" s="2" t="n"/>
-      <c r="N33" s="2" t="n"/>
-      <c r="O33" s="2" t="n"/>
-      <c r="P33" s="2" t="n"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>Chasefu District</t>
+        </is>
+      </c>
       <c r="Q33" s="2" t="n"/>
       <c r="R33" s="2" t="n"/>
       <c r="S33" s="2" t="n"/>
@@ -3790,10 +4236,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
-      <c r="P34" s="2" t="n"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>Mambwe District</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="n"/>
       <c r="R34" s="2" t="n"/>
       <c r="S34" s="2" t="n"/>
@@ -3888,10 +4348,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
-      <c r="P35" s="2" t="n"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>Chadiza District</t>
+        </is>
+      </c>
       <c r="Q35" s="2" t="n"/>
       <c r="R35" s="2" t="n"/>
       <c r="S35" s="2" t="n"/>
@@ -3986,10 +4460,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n"/>
-      <c r="P36" s="2" t="n"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>Lusangazi District</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="n"/>
       <c r="R36" s="2" t="n"/>
       <c r="S36" s="2" t="n"/>
@@ -4084,10 +4572,24 @@
           <t>EasternZambia</t>
         </is>
       </c>
-      <c r="M37" s="2" t="n"/>
-      <c r="N37" s="2" t="n"/>
-      <c r="O37" s="2" t="n"/>
-      <c r="P37" s="2" t="n"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>ZM-03</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>Vubwi District</t>
+        </is>
+      </c>
       <c r="Q37" s="2" t="n"/>
       <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
@@ -4182,10 +4684,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
-      <c r="O38" s="2" t="n"/>
-      <c r="P38" s="2" t="n"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>Mansa District</t>
+        </is>
+      </c>
       <c r="Q38" s="2" t="n"/>
       <c r="R38" s="2" t="n"/>
       <c r="S38" s="2" t="n"/>
@@ -4280,10 +4796,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="n"/>
-      <c r="P39" s="2" t="n"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>Nchelenge District</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="n"/>
       <c r="R39" s="2" t="n"/>
       <c r="S39" s="2" t="n"/>
@@ -4378,10 +4908,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M40" s="3" t="n"/>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="3" t="n"/>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>Chiengi District</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="n"/>
       <c r="R40" s="3" t="n"/>
       <c r="S40" s="3" t="n"/>
@@ -4476,10 +5020,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M41" s="2" t="n"/>
-      <c r="N41" s="2" t="n"/>
-      <c r="O41" s="2" t="n"/>
-      <c r="P41" s="2" t="n"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>Samfya District</t>
+        </is>
+      </c>
       <c r="Q41" s="2" t="n"/>
       <c r="R41" s="2" t="n"/>
       <c r="S41" s="2" t="n"/>
@@ -4574,10 +5132,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M42" s="2" t="n"/>
-      <c r="N42" s="2" t="n"/>
-      <c r="O42" s="2" t="n"/>
-      <c r="P42" s="2" t="n"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>Kawambwa District</t>
+        </is>
+      </c>
       <c r="Q42" s="2" t="n"/>
       <c r="R42" s="2" t="n"/>
       <c r="S42" s="2" t="n"/>
@@ -4672,10 +5244,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M43" s="2" t="n"/>
-      <c r="N43" s="2" t="n"/>
-      <c r="O43" s="2" t="n"/>
-      <c r="P43" s="2" t="n"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>Mwense District</t>
+        </is>
+      </c>
       <c r="Q43" s="2" t="n"/>
       <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
@@ -4770,10 +5356,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M44" s="2" t="n"/>
-      <c r="N44" s="2" t="n"/>
-      <c r="O44" s="2" t="n"/>
-      <c r="P44" s="2" t="n"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>Chifunabuli District</t>
+        </is>
+      </c>
       <c r="Q44" s="2" t="n"/>
       <c r="R44" s="2" t="n"/>
       <c r="S44" s="2" t="n"/>
@@ -4868,10 +5468,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M45" s="2" t="n"/>
-      <c r="N45" s="2" t="n"/>
-      <c r="O45" s="2" t="n"/>
-      <c r="P45" s="2" t="n"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>Mwansabombwe District</t>
+        </is>
+      </c>
       <c r="Q45" s="2" t="n"/>
       <c r="R45" s="2" t="n"/>
       <c r="S45" s="2" t="n"/>
@@ -4966,10 +5580,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M46" s="2" t="n"/>
-      <c r="N46" s="2" t="n"/>
-      <c r="O46" s="2" t="n"/>
-      <c r="P46" s="2" t="n"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>Milenge District</t>
+        </is>
+      </c>
       <c r="Q46" s="2" t="n"/>
       <c r="R46" s="2" t="n"/>
       <c r="S46" s="2" t="n"/>
@@ -5064,10 +5692,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M47" s="2" t="n"/>
-      <c r="N47" s="2" t="n"/>
-      <c r="O47" s="2" t="n"/>
-      <c r="P47" s="2" t="n"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>Chembe District</t>
+        </is>
+      </c>
       <c r="Q47" s="2" t="n"/>
       <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
@@ -5162,10 +5804,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M48" s="2" t="n"/>
-      <c r="N48" s="2" t="n"/>
-      <c r="O48" s="2" t="n"/>
-      <c r="P48" s="2" t="n"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>Chipili District</t>
+        </is>
+      </c>
       <c r="Q48" s="2" t="n"/>
       <c r="R48" s="2" t="n"/>
       <c r="S48" s="2" t="n"/>
@@ -5260,10 +5916,24 @@
           <t>LuapulaZambia</t>
         </is>
       </c>
-      <c r="M49" s="2" t="n"/>
-      <c r="N49" s="2" t="n"/>
-      <c r="O49" s="2" t="n"/>
-      <c r="P49" s="2" t="n"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>ZM-04</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>Lunga District</t>
+        </is>
+      </c>
       <c r="Q49" s="2" t="n"/>
       <c r="R49" s="2" t="n"/>
       <c r="S49" s="2" t="n"/>
@@ -5364,10 +6034,24 @@
           <t>LusakaZambia</t>
         </is>
       </c>
-      <c r="M50" s="2" t="n"/>
-      <c r="N50" s="2" t="n"/>
-      <c r="O50" s="2" t="n"/>
-      <c r="P50" s="2" t="n"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>ZM-09</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>Lusaka District</t>
+        </is>
+      </c>
       <c r="Q50" s="2" t="n"/>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
@@ -5468,10 +6152,24 @@
           <t>LusakaZambia</t>
         </is>
       </c>
-      <c r="M51" s="2" t="n"/>
-      <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="n"/>
-      <c r="P51" s="2" t="n"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>ZM-09</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>Chongwe District</t>
+        </is>
+      </c>
       <c r="Q51" s="2" t="n"/>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
@@ -5572,10 +6270,24 @@
           <t>LusakaZambia</t>
         </is>
       </c>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
-      <c r="O52" s="2" t="n"/>
-      <c r="P52" s="2" t="n"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>ZM-09</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>Chilanga District</t>
+        </is>
+      </c>
       <c r="Q52" s="2" t="n"/>
       <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
@@ -5676,10 +6388,24 @@
           <t>LusakaZambia</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
-      <c r="P53" s="2" t="n"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>ZM-09</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>Kafue District</t>
+        </is>
+      </c>
       <c r="Q53" s="2" t="n"/>
       <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
@@ -5774,10 +6500,24 @@
           <t>LusakaZambia</t>
         </is>
       </c>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="n"/>
-      <c r="O54" s="2" t="n"/>
-      <c r="P54" s="2" t="n"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>ZM-09</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>Rufunsa District</t>
+        </is>
+      </c>
       <c r="Q54" s="2" t="n"/>
       <c r="R54" s="2" t="n"/>
       <c r="S54" s="2" t="n"/>
@@ -5872,10 +6612,24 @@
           <t>LusakaZambia</t>
         </is>
       </c>
-      <c r="M55" s="2" t="n"/>
-      <c r="N55" s="2" t="n"/>
-      <c r="O55" s="2" t="n"/>
-      <c r="P55" s="2" t="n"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>ZM-09</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>Luangwa District</t>
+        </is>
+      </c>
       <c r="Q55" s="2" t="n"/>
       <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
@@ -5970,10 +6724,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M56" s="2" t="n"/>
-      <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
-      <c r="P56" s="2" t="n"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>Nakonde District</t>
+        </is>
+      </c>
       <c r="Q56" s="2" t="n"/>
       <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
@@ -6068,10 +6836,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M57" s="2" t="n"/>
-      <c r="N57" s="2" t="n"/>
-      <c r="O57" s="2" t="n"/>
-      <c r="P57" s="2" t="n"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>Mpika District</t>
+        </is>
+      </c>
       <c r="Q57" s="2" t="n"/>
       <c r="R57" s="2" t="n"/>
       <c r="S57" s="2" t="n"/>
@@ -6166,10 +6948,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M58" s="2" t="n"/>
-      <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="n"/>
-      <c r="P58" s="2" t="n"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>Chinsali District</t>
+        </is>
+      </c>
       <c r="Q58" s="2" t="n"/>
       <c r="R58" s="2" t="n"/>
       <c r="S58" s="2" t="n"/>
@@ -6264,10 +7060,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M59" s="2" t="n"/>
-      <c r="N59" s="2" t="n"/>
-      <c r="O59" s="2" t="n"/>
-      <c r="P59" s="2" t="n"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>Isoka District</t>
+        </is>
+      </c>
       <c r="Q59" s="2" t="n"/>
       <c r="R59" s="2" t="n"/>
       <c r="S59" s="2" t="n"/>
@@ -6362,10 +7172,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M60" s="2" t="n"/>
-      <c r="N60" s="2" t="n"/>
-      <c r="O60" s="2" t="n"/>
-      <c r="P60" s="2" t="n"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>Mafinga District</t>
+        </is>
+      </c>
       <c r="Q60" s="2" t="n"/>
       <c r="R60" s="2" t="n"/>
       <c r="S60" s="2" t="n"/>
@@ -6460,10 +7284,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M61" s="2" t="n"/>
-      <c r="N61" s="2" t="n"/>
-      <c r="O61" s="2" t="n"/>
-      <c r="P61" s="2" t="n"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>Kanchibiya District</t>
+        </is>
+      </c>
       <c r="Q61" s="2" t="n"/>
       <c r="R61" s="2" t="n"/>
       <c r="S61" s="2" t="n"/>
@@ -6558,10 +7396,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M62" s="4" t="n"/>
-      <c r="N62" s="4" t="n"/>
-      <c r="O62" s="4" t="n"/>
-      <c r="P62" s="4" t="n"/>
+      <c r="M62" s="4" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N62" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="O62" s="4" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P62" s="4" t="inlineStr">
+        <is>
+          <t>Shiwa Ng'andu District</t>
+        </is>
+      </c>
       <c r="Q62" s="4" t="n"/>
       <c r="R62" s="4" t="n"/>
       <c r="S62" s="4" t="n"/>
@@ -6656,10 +7508,24 @@
           <t>MuchingaZambia</t>
         </is>
       </c>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="n"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>ZM-10</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>Lavushimanda District</t>
+        </is>
+      </c>
       <c r="Q63" s="2" t="n"/>
       <c r="R63" s="2" t="n"/>
       <c r="S63" s="2" t="n"/>
@@ -6754,10 +7620,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M64" s="2" t="n"/>
-      <c r="N64" s="2" t="n"/>
-      <c r="O64" s="2" t="n"/>
-      <c r="P64" s="2" t="n"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>Kasama District</t>
+        </is>
+      </c>
       <c r="Q64" s="2" t="n"/>
       <c r="R64" s="2" t="n"/>
       <c r="S64" s="2" t="n"/>
@@ -6852,10 +7732,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
-      <c r="O65" s="2" t="n"/>
-      <c r="P65" s="2" t="n"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>Mungwi District</t>
+        </is>
+      </c>
       <c r="Q65" s="2" t="n"/>
       <c r="R65" s="2" t="n"/>
       <c r="S65" s="2" t="n"/>
@@ -6950,10 +7844,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M66" s="2" t="n"/>
-      <c r="N66" s="2" t="n"/>
-      <c r="O66" s="2" t="n"/>
-      <c r="P66" s="2" t="n"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>Mbala District</t>
+        </is>
+      </c>
       <c r="Q66" s="2" t="n"/>
       <c r="R66" s="2" t="n"/>
       <c r="S66" s="2" t="n"/>
@@ -7048,10 +7956,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="n"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>Mpulungu District</t>
+        </is>
+      </c>
       <c r="Q67" s="2" t="n"/>
       <c r="R67" s="2" t="n"/>
       <c r="S67" s="2" t="n"/>
@@ -7146,10 +8068,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>Senga Hill District</t>
+        </is>
+      </c>
       <c r="Q68" s="2" t="n"/>
       <c r="R68" s="2" t="n"/>
       <c r="S68" s="2" t="n"/>
@@ -7244,10 +8180,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M69" s="2" t="n"/>
-      <c r="N69" s="2" t="n"/>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Chilubi District</t>
+        </is>
+      </c>
       <c r="Q69" s="2" t="n"/>
       <c r="R69" s="2" t="n"/>
       <c r="S69" s="2" t="n"/>
@@ -7342,10 +8292,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M70" s="2" t="n"/>
-      <c r="N70" s="2" t="n"/>
-      <c r="O70" s="2" t="n"/>
-      <c r="P70" s="2" t="n"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Kaputa District</t>
+        </is>
+      </c>
       <c r="Q70" s="2" t="n"/>
       <c r="R70" s="2" t="n"/>
       <c r="S70" s="2" t="n"/>
@@ -7440,10 +8404,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M71" s="2" t="n"/>
-      <c r="N71" s="2" t="n"/>
-      <c r="O71" s="2" t="n"/>
-      <c r="P71" s="2" t="n"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Luwingu District</t>
+        </is>
+      </c>
       <c r="Q71" s="2" t="n"/>
       <c r="R71" s="2" t="n"/>
       <c r="S71" s="2" t="n"/>
@@ -7538,10 +8516,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M72" s="2" t="n"/>
-      <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Lunte District</t>
+        </is>
+      </c>
       <c r="Q72" s="2" t="n"/>
       <c r="R72" s="2" t="n"/>
       <c r="S72" s="2" t="n"/>
@@ -7636,10 +8628,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M73" s="2" t="n"/>
-      <c r="N73" s="2" t="n"/>
-      <c r="O73" s="2" t="n"/>
-      <c r="P73" s="2" t="n"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>Lupososhi District</t>
+        </is>
+      </c>
       <c r="Q73" s="2" t="n"/>
       <c r="R73" s="2" t="n"/>
       <c r="S73" s="2" t="n"/>
@@ -7734,10 +8740,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M74" s="2" t="n"/>
-      <c r="N74" s="2" t="n"/>
-      <c r="O74" s="2" t="n"/>
-      <c r="P74" s="2" t="n"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>Nsama District</t>
+        </is>
+      </c>
       <c r="Q74" s="2" t="n"/>
       <c r="R74" s="2" t="n"/>
       <c r="S74" s="2" t="n"/>
@@ -7832,10 +8852,24 @@
           <t>NorthernZambia</t>
         </is>
       </c>
-      <c r="M75" s="2" t="n"/>
-      <c r="N75" s="2" t="n"/>
-      <c r="O75" s="2" t="n"/>
-      <c r="P75" s="2" t="n"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>ZM-05</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>Mporokoso District</t>
+        </is>
+      </c>
       <c r="Q75" s="2" t="n"/>
       <c r="R75" s="2" t="n"/>
       <c r="S75" s="2" t="n"/>
@@ -7930,10 +8964,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M76" s="2" t="n"/>
-      <c r="N76" s="2" t="n"/>
-      <c r="O76" s="2" t="n"/>
-      <c r="P76" s="2" t="n"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>Solwezi District</t>
+        </is>
+      </c>
       <c r="Q76" s="2" t="n"/>
       <c r="R76" s="2" t="n"/>
       <c r="S76" s="2" t="n"/>
@@ -8028,10 +9076,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M77" s="2" t="n"/>
-      <c r="N77" s="2" t="n"/>
-      <c r="O77" s="2" t="n"/>
-      <c r="P77" s="2" t="n"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>Kalumbila District</t>
+        </is>
+      </c>
       <c r="Q77" s="2" t="n"/>
       <c r="R77" s="2" t="n"/>
       <c r="S77" s="2" t="n"/>
@@ -8126,10 +9188,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M78" s="2" t="n"/>
-      <c r="N78" s="2" t="n"/>
-      <c r="O78" s="2" t="n"/>
-      <c r="P78" s="2" t="n"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>Mwinilunga District</t>
+        </is>
+      </c>
       <c r="Q78" s="2" t="n"/>
       <c r="R78" s="2" t="n"/>
       <c r="S78" s="2" t="n"/>
@@ -8224,10 +9300,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M79" s="2" t="n"/>
-      <c r="N79" s="2" t="n"/>
-      <c r="O79" s="2" t="n"/>
-      <c r="P79" s="2" t="n"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>Kasempa District</t>
+        </is>
+      </c>
       <c r="Q79" s="2" t="n"/>
       <c r="R79" s="2" t="n"/>
       <c r="S79" s="2" t="n"/>
@@ -8322,10 +9412,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M80" s="2" t="n"/>
-      <c r="N80" s="2" t="n"/>
-      <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="n"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>Zambezi District</t>
+        </is>
+      </c>
       <c r="Q80" s="2" t="n"/>
       <c r="R80" s="2" t="n"/>
       <c r="S80" s="2" t="n"/>
@@ -8420,10 +9524,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M81" s="2" t="n"/>
-      <c r="N81" s="2" t="n"/>
-      <c r="O81" s="2" t="n"/>
-      <c r="P81" s="2" t="n"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>Mufumbwe District</t>
+        </is>
+      </c>
       <c r="Q81" s="2" t="n"/>
       <c r="R81" s="2" t="n"/>
       <c r="S81" s="2" t="n"/>
@@ -8518,10 +9636,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M82" s="2" t="n"/>
-      <c r="N82" s="2" t="n"/>
-      <c r="O82" s="2" t="n"/>
-      <c r="P82" s="2" t="n"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>Manyinga District</t>
+        </is>
+      </c>
       <c r="Q82" s="2" t="n"/>
       <c r="R82" s="2" t="n"/>
       <c r="S82" s="2" t="n"/>
@@ -8616,10 +9748,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M83" s="2" t="n"/>
-      <c r="N83" s="2" t="n"/>
-      <c r="O83" s="2" t="n"/>
-      <c r="P83" s="2" t="n"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>Kabompo District</t>
+        </is>
+      </c>
       <c r="Q83" s="2" t="n"/>
       <c r="R83" s="2" t="n"/>
       <c r="S83" s="2" t="n"/>
@@ -8714,10 +9860,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M84" s="2" t="n"/>
-      <c r="N84" s="2" t="n"/>
-      <c r="O84" s="2" t="n"/>
-      <c r="P84" s="2" t="n"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>Mushindamo District</t>
+        </is>
+      </c>
       <c r="Q84" s="2" t="n"/>
       <c r="R84" s="2" t="n"/>
       <c r="S84" s="2" t="n"/>
@@ -8812,10 +9972,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M85" s="2" t="n"/>
-      <c r="N85" s="2" t="n"/>
-      <c r="O85" s="2" t="n"/>
-      <c r="P85" s="2" t="n"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>Chavuma District</t>
+        </is>
+      </c>
       <c r="Q85" s="2" t="n"/>
       <c r="R85" s="2" t="n"/>
       <c r="S85" s="2" t="n"/>
@@ -8910,10 +10084,24 @@
           <t>North-WesternZambia</t>
         </is>
       </c>
-      <c r="M86" s="2" t="n"/>
-      <c r="N86" s="2" t="n"/>
-      <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>ZM-06</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>Ikelenge District</t>
+        </is>
+      </c>
       <c r="Q86" s="2" t="n"/>
       <c r="R86" s="2" t="n"/>
       <c r="S86" s="2" t="n"/>
@@ -9014,10 +10202,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M87" s="2" t="n"/>
-      <c r="N87" s="2" t="n"/>
-      <c r="O87" s="2" t="n"/>
-      <c r="P87" s="2" t="n"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>Livingstone District</t>
+        </is>
+      </c>
       <c r="Q87" s="2" t="n"/>
       <c r="R87" s="2" t="n"/>
       <c r="S87" s="2" t="n"/>
@@ -9112,10 +10314,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M88" s="2" t="n"/>
-      <c r="N88" s="2" t="n"/>
-      <c r="O88" s="2" t="n"/>
-      <c r="P88" s="2" t="n"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>Kalomo District</t>
+        </is>
+      </c>
       <c r="Q88" s="2" t="n"/>
       <c r="R88" s="2" t="n"/>
       <c r="S88" s="2" t="n"/>
@@ -9210,10 +10426,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M89" s="2" t="n"/>
-      <c r="N89" s="2" t="n"/>
-      <c r="O89" s="2" t="n"/>
-      <c r="P89" s="2" t="n"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>Monze District</t>
+        </is>
+      </c>
       <c r="Q89" s="2" t="n"/>
       <c r="R89" s="2" t="n"/>
       <c r="S89" s="2" t="n"/>
@@ -9308,10 +10538,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M90" s="2" t="n"/>
-      <c r="N90" s="2" t="n"/>
-      <c r="O90" s="2" t="n"/>
-      <c r="P90" s="2" t="n"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>Choma District</t>
+        </is>
+      </c>
       <c r="Q90" s="2" t="n"/>
       <c r="R90" s="2" t="n"/>
       <c r="S90" s="2" t="n"/>
@@ -9406,10 +10650,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M91" s="2" t="n"/>
-      <c r="N91" s="2" t="n"/>
-      <c r="O91" s="2" t="n"/>
-      <c r="P91" s="2" t="n"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>Mazabuka District</t>
+        </is>
+      </c>
       <c r="Q91" s="2" t="n"/>
       <c r="R91" s="2" t="n"/>
       <c r="S91" s="2" t="n"/>
@@ -9504,10 +10762,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M92" s="2" t="n"/>
-      <c r="N92" s="2" t="n"/>
-      <c r="O92" s="2" t="n"/>
-      <c r="P92" s="2" t="n"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>Kazungula District</t>
+        </is>
+      </c>
       <c r="Q92" s="2" t="n"/>
       <c r="R92" s="2" t="n"/>
       <c r="S92" s="2" t="n"/>
@@ -9602,10 +10874,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M93" s="2" t="n"/>
-      <c r="N93" s="2" t="n"/>
-      <c r="O93" s="2" t="n"/>
-      <c r="P93" s="2" t="n"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>Namwala District</t>
+        </is>
+      </c>
       <c r="Q93" s="2" t="n"/>
       <c r="R93" s="2" t="n"/>
       <c r="S93" s="2" t="n"/>
@@ -9700,10 +10986,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M94" s="2" t="n"/>
-      <c r="N94" s="2" t="n"/>
-      <c r="O94" s="2" t="n"/>
-      <c r="P94" s="2" t="n"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>Sinazongwe District</t>
+        </is>
+      </c>
       <c r="Q94" s="2" t="n"/>
       <c r="R94" s="2" t="n"/>
       <c r="S94" s="2" t="n"/>
@@ -9798,10 +11098,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M95" s="2" t="n"/>
-      <c r="N95" s="2" t="n"/>
-      <c r="O95" s="2" t="n"/>
-      <c r="P95" s="2" t="n"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>Itezhi-Tezhi District</t>
+        </is>
+      </c>
       <c r="Q95" s="2" t="n"/>
       <c r="R95" s="2" t="n"/>
       <c r="S95" s="2" t="n"/>
@@ -9896,10 +11210,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M96" s="2" t="n"/>
-      <c r="N96" s="2" t="n"/>
-      <c r="O96" s="2" t="n"/>
-      <c r="P96" s="2" t="n"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>Zimba District</t>
+        </is>
+      </c>
       <c r="Q96" s="2" t="n"/>
       <c r="R96" s="2" t="n"/>
       <c r="S96" s="2" t="n"/>
@@ -9994,10 +11322,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M97" s="2" t="n"/>
-      <c r="N97" s="2" t="n"/>
-      <c r="O97" s="2" t="n"/>
-      <c r="P97" s="2" t="n"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>Pemba District</t>
+        </is>
+      </c>
       <c r="Q97" s="2" t="n"/>
       <c r="R97" s="2" t="n"/>
       <c r="S97" s="2" t="n"/>
@@ -10092,10 +11434,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M98" s="2" t="n"/>
-      <c r="N98" s="2" t="n"/>
-      <c r="O98" s="2" t="n"/>
-      <c r="P98" s="2" t="n"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>Chikankata District</t>
+        </is>
+      </c>
       <c r="Q98" s="2" t="n"/>
       <c r="R98" s="2" t="n"/>
       <c r="S98" s="2" t="n"/>
@@ -10190,10 +11546,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M99" s="2" t="n"/>
-      <c r="N99" s="2" t="n"/>
-      <c r="O99" s="2" t="n"/>
-      <c r="P99" s="2" t="n"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>Gwembe District</t>
+        </is>
+      </c>
       <c r="Q99" s="2" t="n"/>
       <c r="R99" s="2" t="n"/>
       <c r="S99" s="2" t="n"/>
@@ -10288,10 +11658,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M100" s="2" t="n"/>
-      <c r="N100" s="2" t="n"/>
-      <c r="O100" s="2" t="n"/>
-      <c r="P100" s="2" t="n"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>Chirundu District</t>
+        </is>
+      </c>
       <c r="Q100" s="2" t="n"/>
       <c r="R100" s="2" t="n"/>
       <c r="S100" s="2" t="n"/>
@@ -10386,10 +11770,24 @@
           <t>SouthernZambia</t>
         </is>
       </c>
-      <c r="M101" s="2" t="n"/>
-      <c r="N101" s="2" t="n"/>
-      <c r="O101" s="2" t="n"/>
-      <c r="P101" s="2" t="n"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>ZM-07</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>Siavonga District</t>
+        </is>
+      </c>
       <c r="Q101" s="2" t="n"/>
       <c r="R101" s="2" t="n"/>
       <c r="S101" s="2" t="n"/>
@@ -10484,10 +11882,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M102" s="2" t="n"/>
-      <c r="N102" s="2" t="n"/>
-      <c r="O102" s="2" t="n"/>
-      <c r="P102" s="2" t="n"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>Mongu District</t>
+        </is>
+      </c>
       <c r="Q102" s="2" t="n"/>
       <c r="R102" s="2" t="n"/>
       <c r="S102" s="2" t="n"/>
@@ -10582,10 +11994,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M103" s="2" t="n"/>
-      <c r="N103" s="2" t="n"/>
-      <c r="O103" s="2" t="n"/>
-      <c r="P103" s="2" t="n"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>Kaoma District</t>
+        </is>
+      </c>
       <c r="Q103" s="2" t="n"/>
       <c r="R103" s="2" t="n"/>
       <c r="S103" s="2" t="n"/>
@@ -10680,10 +12106,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="2" t="n"/>
-      <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>Senanga District</t>
+        </is>
+      </c>
       <c r="Q104" s="2" t="n"/>
       <c r="R104" s="2" t="n"/>
       <c r="S104" s="2" t="n"/>
@@ -10778,10 +12218,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M105" s="2" t="n"/>
-      <c r="N105" s="2" t="n"/>
-      <c r="O105" s="2" t="n"/>
-      <c r="P105" s="2" t="n"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>Kalabo District</t>
+        </is>
+      </c>
       <c r="Q105" s="2" t="n"/>
       <c r="R105" s="2" t="n"/>
       <c r="S105" s="2" t="n"/>
@@ -10876,10 +12330,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M106" s="2" t="n"/>
-      <c r="N106" s="2" t="n"/>
-      <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>Nkeyema District</t>
+        </is>
+      </c>
       <c r="Q106" s="2" t="n"/>
       <c r="R106" s="2" t="n"/>
       <c r="S106" s="2" t="n"/>
@@ -10974,10 +12442,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M107" s="2" t="n"/>
-      <c r="N107" s="2" t="n"/>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P107" s="2" t="inlineStr">
+        <is>
+          <t>Lukulu District</t>
+        </is>
+      </c>
       <c r="Q107" s="2" t="n"/>
       <c r="R107" s="2" t="n"/>
       <c r="S107" s="2" t="n"/>
@@ -11072,10 +12554,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M108" s="2" t="n"/>
-      <c r="N108" s="2" t="n"/>
-      <c r="O108" s="2" t="n"/>
-      <c r="P108" s="2" t="n"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>Shang'ombo District</t>
+        </is>
+      </c>
       <c r="Q108" s="2" t="n"/>
       <c r="R108" s="2" t="n"/>
       <c r="S108" s="2" t="n"/>
@@ -11170,10 +12666,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M109" s="2" t="n"/>
-      <c r="N109" s="2" t="n"/>
-      <c r="O109" s="2" t="n"/>
-      <c r="P109" s="2" t="n"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N109" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P109" s="2" t="inlineStr">
+        <is>
+          <t>Nalolo District</t>
+        </is>
+      </c>
       <c r="Q109" s="2" t="n"/>
       <c r="R109" s="2" t="n"/>
       <c r="S109" s="2" t="n"/>
@@ -11268,10 +12778,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M110" s="2" t="n"/>
-      <c r="N110" s="2" t="n"/>
-      <c r="O110" s="2" t="n"/>
-      <c r="P110" s="2" t="n"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N110" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O110" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P110" s="2" t="inlineStr">
+        <is>
+          <t>Sesheke District</t>
+        </is>
+      </c>
       <c r="Q110" s="2" t="n"/>
       <c r="R110" s="2" t="n"/>
       <c r="S110" s="2" t="n"/>
@@ -11366,10 +12890,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="n"/>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O111" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P111" s="2" t="inlineStr">
+        <is>
+          <t>Sioma District</t>
+        </is>
+      </c>
       <c r="Q111" s="2" t="n"/>
       <c r="R111" s="2" t="n"/>
       <c r="S111" s="2" t="n"/>
@@ -11464,10 +13002,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M112" s="2" t="n"/>
-      <c r="N112" s="2" t="n"/>
-      <c r="O112" s="2" t="n"/>
-      <c r="P112" s="2" t="n"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N112" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O112" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P112" s="2" t="inlineStr">
+        <is>
+          <t>Limulunga District</t>
+        </is>
+      </c>
       <c r="Q112" s="2" t="n"/>
       <c r="R112" s="2" t="n"/>
       <c r="S112" s="2" t="n"/>
@@ -11562,10 +13114,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M113" s="2" t="n"/>
-      <c r="N113" s="2" t="n"/>
-      <c r="O113" s="2" t="n"/>
-      <c r="P113" s="2" t="n"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N113" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P113" s="2" t="inlineStr">
+        <is>
+          <t>Luampa District</t>
+        </is>
+      </c>
       <c r="Q113" s="2" t="n"/>
       <c r="R113" s="2" t="n"/>
       <c r="S113" s="2" t="n"/>
@@ -11660,10 +13226,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M114" s="2" t="n"/>
-      <c r="N114" s="2" t="n"/>
-      <c r="O114" s="2" t="n"/>
-      <c r="P114" s="2" t="n"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P114" s="2" t="inlineStr">
+        <is>
+          <t>Sikongo District</t>
+        </is>
+      </c>
       <c r="Q114" s="2" t="n"/>
       <c r="R114" s="2" t="n"/>
       <c r="S114" s="2" t="n"/>
@@ -11758,10 +13338,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M115" s="2" t="n"/>
-      <c r="N115" s="2" t="n"/>
-      <c r="O115" s="2" t="n"/>
-      <c r="P115" s="2" t="n"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P115" s="2" t="inlineStr">
+        <is>
+          <t>Mulobezi District</t>
+        </is>
+      </c>
       <c r="Q115" s="2" t="n"/>
       <c r="R115" s="2" t="n"/>
       <c r="S115" s="2" t="n"/>
@@ -11856,10 +13450,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M116" s="2" t="n"/>
-      <c r="N116" s="2" t="n"/>
-      <c r="O116" s="2" t="n"/>
-      <c r="P116" s="2" t="n"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P116" s="2" t="inlineStr">
+        <is>
+          <t>Mwandi District</t>
+        </is>
+      </c>
       <c r="Q116" s="2" t="n"/>
       <c r="R116" s="2" t="n"/>
       <c r="S116" s="2" t="n"/>
@@ -11954,10 +13562,24 @@
           <t>WesternZambia</t>
         </is>
       </c>
-      <c r="M117" s="2" t="n"/>
-      <c r="N117" s="2" t="n"/>
-      <c r="O117" s="2" t="n"/>
-      <c r="P117" s="2" t="n"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>county</t>
+        </is>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>ZM-01</t>
+        </is>
+      </c>
+      <c r="P117" s="2" t="inlineStr">
+        <is>
+          <t>Mitete District</t>
+        </is>
+      </c>
       <c r="Q117" s="2" t="n"/>
       <c r="R117" s="2" t="n"/>
       <c r="S117" s="2" t="n"/>
